--- a/customer-stories/Customer_Stories_PlanB.xlsx
+++ b/customer-stories/Customer_Stories_PlanB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flaviamendeztsutsumi/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flaviamendeztsutsumi/Desktop/ISO/ISW-Practica/customer-stories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73C62AC9-6876-2546-9D2C-3A65168DECEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8204B592-D8D3-9B46-8891-94C9F863B0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="680" windowWidth="29900" windowHeight="19900" tabRatio="500" firstSheet="38" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4300" yWindow="680" windowWidth="29900" windowHeight="19900" tabRatio="500" firstSheet="54" activeTab="57" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="1" r:id="rId1"/>
@@ -9239,7 +9239,7 @@
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="8">
         <v>6</v>
       </c>
       <c r="C8" s="10"/>
@@ -9895,7 +9895,7 @@
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="8">
         <v>5</v>
       </c>
       <c r="C8" s="10"/>
@@ -10225,7 +10225,7 @@
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="8">
         <v>6</v>
       </c>
       <c r="C8" s="10"/>

--- a/customer-stories/Customer_Stories_PlanB.xlsx
+++ b/customer-stories/Customer_Stories_PlanB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mattp\dev\school\3-GISI\ISW-Practica\customer-stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F76862E-EC88-4E63-86DF-23295D001E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985E4E03-3AEB-4303-96EC-559D273C4A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="739" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="292">
   <si>
     <t>#</t>
   </si>
@@ -947,6 +947,18 @@
   </si>
   <si>
     <t>LUC10</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>IM</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1108,1928 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="192">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -2415,6 +4348,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="149" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="148" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="147" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
   </hyperlinks>
@@ -2580,6 +4524,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="146" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="145" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="144" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
   </hyperlinks>
@@ -2745,6 +4700,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="143" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="142" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="141" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
   </hyperlinks>
@@ -2910,6 +4876,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="140" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="139" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="138" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
   </hyperlinks>
@@ -3075,6 +5052,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="137" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="136" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="135" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
   </hyperlinks>
@@ -3240,6 +5228,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="134" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="133" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="132" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0E00-000000000000}"/>
   </hyperlinks>
@@ -3405,6 +5404,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="131" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="130" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="129" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
   </hyperlinks>
@@ -3570,6 +5580,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="128" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="127" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="126" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1000-000000000000}"/>
   </hyperlinks>
@@ -3735,6 +5756,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="125" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="124" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="123" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
   </hyperlinks>
@@ -3900,6 +5932,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="122" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="121" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="120" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1200-000000000000}"/>
   </hyperlinks>
@@ -4065,6 +6108,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="173" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="172" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="171" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
@@ -4230,6 +6284,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="119" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="118" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="117" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1300-000000000000}"/>
   </hyperlinks>
@@ -4395,6 +6460,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="116" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="115" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="114" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1400-000000000000}"/>
   </hyperlinks>
@@ -4560,6 +6636,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="113" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="112" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="111" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1500-000000000000}"/>
   </hyperlinks>
@@ -4727,6 +6814,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="110" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="109" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="108" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1600-000000000000}"/>
   </hyperlinks>
@@ -4890,6 +6988,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="107" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="106" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="105" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1700-000000000000}"/>
   </hyperlinks>
@@ -5057,6 +7166,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="104" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="103" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="102" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1800-000000000000}"/>
   </hyperlinks>
@@ -5224,6 +7344,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="101" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="100" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="99" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1900-000000000000}"/>
   </hyperlinks>
@@ -5387,6 +7518,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="98" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="97" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="96" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1A00-000000000000}"/>
   </hyperlinks>
@@ -5452,21 +7594,27 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>290</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>223</v>
+      </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="8">
+        <v>13</v>
+      </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -5550,6 +7698,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="95" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="94" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="93" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1B00-000000000000}"/>
   </hyperlinks>
@@ -5717,6 +7876,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="92" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="91" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="90" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1C00-000000000000}"/>
   </hyperlinks>
@@ -5882,6 +8052,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="170" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="169" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="168" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
@@ -6045,6 +8226,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="89" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="88" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="87" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1D00-000000000000}"/>
   </hyperlinks>
@@ -6110,21 +8302,27 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>226</v>
+      </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="8">
+        <v>7</v>
+      </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -6208,6 +8406,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="86" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="85" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="84" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1E00-000000000000}"/>
   </hyperlinks>
@@ -6371,6 +8580,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="83" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="82" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="81" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-1F00-000000000000}"/>
   </hyperlinks>
@@ -6534,6 +8754,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="80" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="79" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="78" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2000-000000000000}"/>
   </hyperlinks>
@@ -6599,21 +8830,27 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>226</v>
+      </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="8">
+        <v>4</v>
+      </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -6697,6 +8934,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="77" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="76" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="75" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2100-000000000000}"/>
   </hyperlinks>
@@ -6860,6 +9108,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="74" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="73" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="72" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2200-000000000000}"/>
   </hyperlinks>
@@ -7023,6 +9282,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="71" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="70" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="69" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2300-000000000000}"/>
   </hyperlinks>
@@ -7088,21 +9358,27 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>290</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>226</v>
+      </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="8">
+        <v>6</v>
+      </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -7186,6 +9462,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="68" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="67" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="66" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2400-000000000000}"/>
   </hyperlinks>
@@ -7349,6 +9636,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="65" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="64" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="63" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2500-000000000000}"/>
   </hyperlinks>
@@ -7512,6 +9810,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="62" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="61" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="60" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2600-000000000000}"/>
   </hyperlinks>
@@ -7677,6 +9986,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="167" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="166" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="165" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
@@ -7840,6 +10160,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="59" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="58" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="57" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2700-000000000000}"/>
   </hyperlinks>
@@ -8007,6 +10338,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="56" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="55" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2800-000000000000}"/>
   </hyperlinks>
@@ -8170,6 +10512,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="53" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="52" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="51" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2900-000000000000}"/>
   </hyperlinks>
@@ -8337,6 +10690,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="50" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="49" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="48" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2A00-000000000000}"/>
   </hyperlinks>
@@ -8500,6 +10864,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="47" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="46" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="45" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2B00-000000000000}"/>
   </hyperlinks>
@@ -8565,7 +10940,9 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>288</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8663,6 +11040,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="44" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="43" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="42" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2C00-000000000000}"/>
   </hyperlinks>
@@ -8826,6 +11214,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="41" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="39" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2D00-000000000000}"/>
   </hyperlinks>
@@ -8989,6 +11388,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2E00-000000000000}"/>
   </hyperlinks>
@@ -9152,6 +11562,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="35" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-2F00-000000000000}"/>
   </hyperlinks>
@@ -9315,6 +11736,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="32" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3000-000000000000}"/>
   </hyperlinks>
@@ -9480,6 +11912,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="164" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="163" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="162" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
@@ -9647,6 +12090,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3100-000000000000}"/>
   </hyperlinks>
@@ -9814,6 +12268,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3200-000000000000}"/>
   </hyperlinks>
@@ -9977,6 +12442,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3300-000000000000}"/>
   </hyperlinks>
@@ -10140,6 +12616,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3400-000000000000}"/>
   </hyperlinks>
@@ -10303,6 +12790,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3500-000000000000}"/>
   </hyperlinks>
@@ -10470,6 +12968,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3600-000000000000}"/>
   </hyperlinks>
@@ -10633,6 +13142,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3700-000000000000}"/>
   </hyperlinks>
@@ -10800,6 +13320,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3800-000000000000}"/>
   </hyperlinks>
@@ -10865,21 +13396,27 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>226</v>
+      </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="8">
+        <v>3</v>
+      </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -10963,6 +13500,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3900-000000000000}"/>
   </hyperlinks>
@@ -11126,11 +13674,22 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-3A00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11291,6 +13850,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="161" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="160" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="159" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
   </hyperlinks>
@@ -11358,7 +13928,9 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>291</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -11456,6 +14028,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="158" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="157" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="156" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
   </hyperlinks>
@@ -11621,6 +14204,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="155" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="154" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="153" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
   </hyperlinks>
@@ -11786,6 +14380,17 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C18"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="containsText" dxfId="152" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="151" priority="2" operator="containsText" text="N">
+      <formula>NOT(ISERROR(SEARCH("N",B6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="150" priority="3" operator="containsText" text="M">
+      <formula>NOT(ISERROR(SEARCH("M",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A19" location="Índice!A1" display="↑ Volver al índice" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
   </hyperlinks>

--- a/customer-stories/Customer_Stories_PlanB.xlsx
+++ b/customer-stories/Customer_Stories_PlanB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mattp\dev\school\3-GISI\ISW-Practica\customer-stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985E4E03-3AEB-4303-96EC-559D273C4A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651D4C6A-606D-449F-AF14-1CF105D5BFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="739" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="739" firstSheet="51" activeTab="52" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="293">
   <si>
     <t>#</t>
   </si>
@@ -959,6 +959,9 @@
   </si>
   <si>
     <t>IM</t>
+  </si>
+  <si>
+    <t>Medio Bajo</t>
   </si>
 </sst>
 </file>
@@ -7420,21 +7423,27 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>223</v>
+      </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="6">
+        <v>20</v>
+      </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -8128,7 +8137,9 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>288</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -11464,21 +11475,27 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>226</v>
+      </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="8">
+        <v>4</v>
+      </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -11988,7 +12005,9 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -11996,7 +12015,7 @@
         <v>68</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>226</v>
+        <v>292</v>
       </c>
       <c r="C7" s="10"/>
     </row>
@@ -12518,7 +12537,9 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>288</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -13044,21 +13065,27 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>226</v>
+      </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="8">
+        <v>3</v>
+      </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -13576,7 +13603,9 @@
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>288</v>
+      </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">

--- a/customer-stories/Customer_Stories_PlanB.xlsx
+++ b/customer-stories/Customer_Stories_PlanB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mattp\dev\school\3-GISI\ISW-Practica\customer-stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651D4C6A-606D-449F-AF14-1CF105D5BFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1CCF01-15BC-49A2-9F39-BFE2FA5BB9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="739" firstSheet="51" activeTab="52" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="739" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="1" r:id="rId1"/>
@@ -1009,7 +1009,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1026,6 +1026,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE6F1"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1069,7 +1075,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1107,6 +1113,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3970,7 +3977,7 @@
       <c r="C48" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="15" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3998,7 +4005,7 @@
       <c r="C50" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="15" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4110,7 +4117,7 @@
       <c r="C58" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="15" t="s">
         <v>59</v>
       </c>
     </row>

--- a/customer-stories/Customer_Stories_PlanB.xlsx
+++ b/customer-stories/Customer_Stories_PlanB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flaviamendeztsutsumi/Desktop/ISO/ISW-Practica/customer-stories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62472ABF-7B90-4F43-A592-C036C943E092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B66F25C-0F18-704B-B571-81E80FB2043C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" tabRatio="500" firstSheet="48" activeTab="49" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4300" yWindow="680" windowWidth="29900" windowHeight="19900" tabRatio="500" firstSheet="46" activeTab="47" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="322">
   <si>
     <t>#</t>
   </si>
@@ -1294,12 +1294,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1308,9 +1302,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1322,9 +1313,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1339,6 +1327,18 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4143,10 +4143,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -4158,7 +4158,7 @@
       <c r="B2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -4167,7 +4167,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -4176,7 +4176,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -4185,28 +4185,28 @@
       <c r="B5" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -4215,7 +4215,7 @@
       <c r="B9" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -4224,59 +4224,59 @@
       <c r="B10" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -4319,10 +4319,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -4334,7 +4334,7 @@
       <c r="B2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -4343,7 +4343,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -4352,7 +4352,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -4361,7 +4361,7 @@
       <c r="B5" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -4370,7 +4370,7 @@
       <c r="B6" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -4379,7 +4379,7 @@
       <c r="B7" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -4388,7 +4388,7 @@
       <c r="B8" s="11">
         <v>7</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -4397,7 +4397,7 @@
       <c r="B9" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -4406,59 +4406,59 @@
       <c r="B10" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -4501,10 +4501,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -4516,7 +4516,7 @@
       <c r="B2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -4525,7 +4525,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -4534,7 +4534,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -4543,7 +4543,7 @@
       <c r="B5" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -4552,7 +4552,7 @@
       <c r="B6" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -4561,7 +4561,7 @@
       <c r="B7" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -4570,7 +4570,7 @@
       <c r="B8" s="11">
         <v>20</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -4579,7 +4579,7 @@
       <c r="B9" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -4588,59 +4588,59 @@
       <c r="B10" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -4683,10 +4683,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -4698,7 +4698,7 @@
       <c r="B2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -4707,7 +4707,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -4716,7 +4716,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -4725,28 +4725,28 @@
       <c r="B5" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -4755,7 +4755,7 @@
       <c r="B9" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -4764,59 +4764,59 @@
       <c r="B10" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -4859,10 +4859,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -4874,7 +4874,7 @@
       <c r="B2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -4883,7 +4883,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -4892,7 +4892,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -4901,7 +4901,7 @@
       <c r="B5" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -4910,7 +4910,7 @@
       <c r="B6" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -4919,7 +4919,7 @@
       <c r="B7" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -4928,7 +4928,7 @@
       <c r="B8" s="11">
         <v>20</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -4937,7 +4937,7 @@
       <c r="B9" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -4946,59 +4946,59 @@
       <c r="B10" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5041,10 +5041,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5056,7 +5056,7 @@
       <c r="B2" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5065,7 +5065,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5074,7 +5074,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5083,7 +5083,7 @@
       <c r="B5" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -5092,7 +5092,7 @@
       <c r="B6" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -5101,7 +5101,7 @@
       <c r="B7" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -5110,7 +5110,7 @@
       <c r="B8" s="11">
         <v>20</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -5119,7 +5119,7 @@
       <c r="B9" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -5128,59 +5128,59 @@
       <c r="B10" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5223,10 +5223,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5238,7 +5238,7 @@
       <c r="B2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5247,7 +5247,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5256,7 +5256,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5265,28 +5265,28 @@
       <c r="B5" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -5295,7 +5295,7 @@
       <c r="B9" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -5304,59 +5304,59 @@
       <c r="B10" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5399,10 +5399,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5414,7 +5414,7 @@
       <c r="B2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5423,7 +5423,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5432,7 +5432,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5441,28 +5441,28 @@
       <c r="B5" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -5471,7 +5471,7 @@
       <c r="B9" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -5480,59 +5480,59 @@
       <c r="B10" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5575,10 +5575,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5590,7 +5590,7 @@
       <c r="B2" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5599,7 +5599,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5608,7 +5608,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5617,7 +5617,7 @@
       <c r="B5" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -5626,7 +5626,7 @@
       <c r="B6" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -5635,7 +5635,7 @@
       <c r="B7" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -5644,7 +5644,7 @@
       <c r="B8" s="11">
         <v>40</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -5653,7 +5653,7 @@
       <c r="B9" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -5662,59 +5662,59 @@
       <c r="B10" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5757,10 +5757,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5772,7 +5772,7 @@
       <c r="B2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5781,7 +5781,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5790,7 +5790,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5799,28 +5799,28 @@
       <c r="B5" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -5829,7 +5829,7 @@
       <c r="B9" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -5838,59 +5838,59 @@
       <c r="B10" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5933,10 +5933,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5948,7 +5948,7 @@
       <c r="B2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5957,7 +5957,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5966,7 +5966,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5975,28 +5975,28 @@
       <c r="B5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6005,7 +6005,7 @@
       <c r="B9" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6014,59 +6014,59 @@
       <c r="B10" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6109,10 +6109,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -6124,7 +6124,7 @@
       <c r="B2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -6133,7 +6133,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -6142,7 +6142,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -6151,28 +6151,28 @@
       <c r="B5" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6181,7 +6181,7 @@
       <c r="B9" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6190,59 +6190,59 @@
       <c r="B10" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6285,10 +6285,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -6300,7 +6300,7 @@
       <c r="B2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -6309,7 +6309,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -6318,7 +6318,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -6327,7 +6327,7 @@
       <c r="B5" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -6336,7 +6336,7 @@
       <c r="B6" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -6345,7 +6345,7 @@
       <c r="B7" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -6354,7 +6354,7 @@
       <c r="B8" s="11">
         <v>5</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6363,7 +6363,7 @@
       <c r="B9" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6372,59 +6372,59 @@
       <c r="B10" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6467,10 +6467,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -6482,7 +6482,7 @@
       <c r="B2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -6491,7 +6491,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -6500,7 +6500,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -6509,28 +6509,28 @@
       <c r="B5" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6539,7 +6539,7 @@
       <c r="B9" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6548,59 +6548,59 @@
       <c r="B10" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6643,10 +6643,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -6658,7 +6658,7 @@
       <c r="B2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -6667,7 +6667,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -6676,21 +6676,21 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -6699,7 +6699,7 @@
       <c r="B7" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -6708,7 +6708,7 @@
       <c r="B8" s="13">
         <v>7</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6717,7 +6717,7 @@
       <c r="B9" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6726,59 +6726,59 @@
       <c r="B10" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6821,10 +6821,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -6836,7 +6836,7 @@
       <c r="B2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -6845,7 +6845,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -6854,35 +6854,35 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6891,7 +6891,7 @@
       <c r="B9" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6900,59 +6900,59 @@
       <c r="B10" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6995,10 +6995,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7010,7 +7010,7 @@
       <c r="B2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7019,7 +7019,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7028,21 +7028,21 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -7051,7 +7051,7 @@
       <c r="B7" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -7060,7 +7060,7 @@
       <c r="B8" s="13">
         <v>8</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7069,7 +7069,7 @@
       <c r="B9" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7078,59 +7078,59 @@
       <c r="B10" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -7173,10 +7173,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7188,7 +7188,7 @@
       <c r="B2" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7197,7 +7197,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7206,21 +7206,21 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -7229,7 +7229,7 @@
       <c r="B7" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -7238,7 +7238,7 @@
       <c r="B8" s="13">
         <v>10</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7247,7 +7247,7 @@
       <c r="B9" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7256,59 +7256,59 @@
       <c r="B10" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -7351,10 +7351,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7366,7 +7366,7 @@
       <c r="B2" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7375,7 +7375,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7384,14 +7384,14 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -7400,7 +7400,7 @@
       <c r="B6" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -7409,7 +7409,7 @@
       <c r="B7" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -7418,7 +7418,7 @@
       <c r="B8" s="11">
         <v>20</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7427,7 +7427,7 @@
       <c r="B9" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7436,59 +7436,59 @@
       <c r="B10" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -7531,10 +7531,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7546,7 +7546,7 @@
       <c r="B2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7555,7 +7555,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7564,14 +7564,14 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -7580,7 +7580,7 @@
       <c r="B6" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -7589,7 +7589,7 @@
       <c r="B7" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -7598,7 +7598,7 @@
       <c r="B8" s="13">
         <v>13</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7607,7 +7607,7 @@
       <c r="B9" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7616,59 +7616,59 @@
       <c r="B10" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -7711,10 +7711,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7726,7 +7726,7 @@
       <c r="B2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7735,7 +7735,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7744,21 +7744,21 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -7767,7 +7767,7 @@
       <c r="B7" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -7776,7 +7776,7 @@
       <c r="B8" s="13">
         <v>6</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7785,7 +7785,7 @@
       <c r="B9" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7794,59 +7794,59 @@
       <c r="B10" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -7889,10 +7889,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7904,7 +7904,7 @@
       <c r="B2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7913,7 +7913,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7922,7 +7922,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -7931,28 +7931,28 @@
       <c r="B5" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7961,7 +7961,7 @@
       <c r="B9" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7970,59 +7970,59 @@
       <c r="B10" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8065,10 +8065,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8080,7 +8080,7 @@
       <c r="B2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8089,7 +8089,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8098,14 +8098,14 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -8114,21 +8114,21 @@
       <c r="B6" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -8137,7 +8137,7 @@
       <c r="B9" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -8146,59 +8146,59 @@
       <c r="B10" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8241,10 +8241,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8256,7 +8256,7 @@
       <c r="B2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8265,7 +8265,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8274,14 +8274,14 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -8290,7 +8290,7 @@
       <c r="B6" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -8299,7 +8299,7 @@
       <c r="B7" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -8308,7 +8308,7 @@
       <c r="B8" s="13">
         <v>7</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -8317,7 +8317,7 @@
       <c r="B9" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -8326,59 +8326,59 @@
       <c r="B10" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8421,10 +8421,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8436,7 +8436,7 @@
       <c r="B2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8445,7 +8445,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8454,35 +8454,35 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -8491,7 +8491,7 @@
       <c r="B9" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -8500,59 +8500,59 @@
       <c r="B10" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8595,10 +8595,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8610,7 +8610,7 @@
       <c r="B2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8619,7 +8619,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8628,14 +8628,14 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -8644,7 +8644,7 @@
       <c r="B6" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -8653,7 +8653,7 @@
       <c r="B7" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -8662,7 +8662,7 @@
       <c r="B8" s="11">
         <v>8</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -8671,7 +8671,7 @@
       <c r="B9" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -8680,59 +8680,59 @@
       <c r="B10" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8775,10 +8775,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8790,7 +8790,7 @@
       <c r="B2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8799,7 +8799,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8808,14 +8808,14 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -8824,7 +8824,7 @@
       <c r="B6" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -8833,7 +8833,7 @@
       <c r="B7" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -8842,7 +8842,7 @@
       <c r="B8" s="13">
         <v>4</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -8851,7 +8851,7 @@
       <c r="B9" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -8860,59 +8860,59 @@
       <c r="B10" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8955,10 +8955,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8970,7 +8970,7 @@
       <c r="B2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8979,7 +8979,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8988,35 +8988,35 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9025,7 +9025,7 @@
       <c r="B9" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9034,59 +9034,59 @@
       <c r="B10" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9129,10 +9129,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -9144,7 +9144,7 @@
       <c r="B2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -9153,7 +9153,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -9162,14 +9162,14 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -9178,7 +9178,7 @@
       <c r="B6" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -9187,7 +9187,7 @@
       <c r="B7" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -9196,7 +9196,7 @@
       <c r="B8" s="11">
         <v>8</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9205,7 +9205,7 @@
       <c r="B9" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9214,59 +9214,59 @@
       <c r="B10" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9309,10 +9309,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -9324,7 +9324,7 @@
       <c r="B2" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -9333,7 +9333,7 @@
       <c r="B3" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -9342,14 +9342,14 @@
       <c r="B4" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -9358,7 +9358,7 @@
       <c r="B6" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -9367,7 +9367,7 @@
       <c r="B7" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -9376,7 +9376,7 @@
       <c r="B8" s="13">
         <v>6</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9385,7 +9385,7 @@
       <c r="B9" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9394,59 +9394,59 @@
       <c r="B10" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9489,10 +9489,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -9504,7 +9504,7 @@
       <c r="B2" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -9513,14 +9513,14 @@
       <c r="B3" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -9529,28 +9529,28 @@
       <c r="B5" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9559,7 +9559,7 @@
       <c r="B9" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9568,59 +9568,59 @@
       <c r="B10" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9663,10 +9663,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -9678,7 +9678,7 @@
       <c r="B2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -9687,14 +9687,14 @@
       <c r="B3" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -9703,28 +9703,28 @@
       <c r="B5" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9733,7 +9733,7 @@
       <c r="B9" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9742,59 +9742,59 @@
       <c r="B10" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9837,10 +9837,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -9852,7 +9852,7 @@
       <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -9861,7 +9861,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -9870,7 +9870,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -9879,28 +9879,28 @@
       <c r="B5" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9909,7 +9909,7 @@
       <c r="B9" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9918,59 +9918,59 @@
       <c r="B10" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10013,10 +10013,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10028,7 +10028,7 @@
       <c r="B2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10037,14 +10037,14 @@
       <c r="B3" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -10053,28 +10053,28 @@
       <c r="B5" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10083,7 +10083,7 @@
       <c r="B9" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10092,59 +10092,59 @@
       <c r="B10" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10187,10 +10187,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10202,7 +10202,7 @@
       <c r="B2" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10211,14 +10211,14 @@
       <c r="B3" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -10227,14 +10227,14 @@
       <c r="B5" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -10243,7 +10243,7 @@
       <c r="B7" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -10252,7 +10252,7 @@
       <c r="B8" s="13">
         <v>5</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10261,7 +10261,7 @@
       <c r="B9" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10270,59 +10270,59 @@
       <c r="B10" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10365,10 +10365,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10380,7 +10380,7 @@
       <c r="B2" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10389,14 +10389,14 @@
       <c r="B3" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -10405,28 +10405,28 @@
       <c r="B5" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10435,7 +10435,7 @@
       <c r="B9" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10444,59 +10444,59 @@
       <c r="B10" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10539,10 +10539,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10554,7 +10554,7 @@
       <c r="B2" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10563,14 +10563,14 @@
       <c r="B3" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -10579,14 +10579,14 @@
       <c r="B5" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -10595,7 +10595,7 @@
       <c r="B7" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -10604,7 +10604,7 @@
       <c r="B8" s="13">
         <v>10</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10613,7 +10613,7 @@
       <c r="B9" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10622,59 +10622,59 @@
       <c r="B10" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10717,10 +10717,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10732,7 +10732,7 @@
       <c r="B2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10741,7 +10741,7 @@
       <c r="B3" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -10750,35 +10750,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10787,7 +10787,7 @@
       <c r="B9" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10796,59 +10796,59 @@
       <c r="B10" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10891,10 +10891,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10906,7 +10906,7 @@
       <c r="B2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10915,7 +10915,7 @@
       <c r="B3" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -10924,14 +10924,14 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -10940,21 +10940,21 @@
       <c r="B6" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10963,7 +10963,7 @@
       <c r="B9" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10972,59 +10972,59 @@
       <c r="B10" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -11067,10 +11067,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -11082,7 +11082,7 @@
       <c r="B2" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -11091,7 +11091,7 @@
       <c r="B3" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -11100,35 +11100,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -11137,7 +11137,7 @@
       <c r="B9" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -11146,59 +11146,59 @@
       <c r="B10" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -11241,10 +11241,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -11256,7 +11256,7 @@
       <c r="B2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -11265,7 +11265,7 @@
       <c r="B3" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -11274,35 +11274,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -11311,7 +11311,7 @@
       <c r="B9" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -11320,59 +11320,59 @@
       <c r="B10" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -11415,10 +11415,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -11427,183 +11427,185 @@
       <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="18"/>
+      <c r="C2" s="16"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="C3" s="18"/>
+      <c r="C3" s="16"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="18"/>
+      <c r="C4" s="16"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="18"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="16"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="18"/>
+      <c r="C6" s="16"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="18"/>
+      <c r="C7" s="16"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="15">
         <v>4</v>
       </c>
-      <c r="C8" s="18"/>
+      <c r="C8" s="16"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C9" s="18"/>
+      <c r="C9" s="16"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="C10" s="18"/>
+      <c r="C10" s="16"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="17" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="C13" s="18"/>
+      <c r="C13" s="16"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="22" t="s">
         <v>296</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="17" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="17"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="22" t="s">
         <v>298</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="17"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="22" t="s">
         <v>299</v>
       </c>
-      <c r="C17" s="19"/>
+      <c r="C17" s="17"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="17" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="C19" s="18"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="C20" s="18"/>
+      <c r="C20" s="17" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="22" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="24"/>
+      <c r="C21" s="30"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
@@ -11645,10 +11647,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -11660,7 +11662,7 @@
       <c r="B2" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -11669,7 +11671,7 @@
       <c r="B3" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -11678,35 +11680,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -11715,7 +11717,7 @@
       <c r="B9" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -11724,59 +11726,59 @@
       <c r="B10" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -11819,10 +11821,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -11834,7 +11836,7 @@
       <c r="B2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -11843,7 +11845,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -11852,7 +11854,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -11861,7 +11863,7 @@
       <c r="B5" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -11870,7 +11872,7 @@
       <c r="B6" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -11879,7 +11881,7 @@
       <c r="B7" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -11888,7 +11890,7 @@
       <c r="B8" s="11">
         <v>5</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -11897,7 +11899,7 @@
       <c r="B9" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -11906,59 +11908,59 @@
       <c r="B10" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -12001,10 +12003,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12016,7 +12018,7 @@
       <c r="B2" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12025,7 +12027,7 @@
       <c r="B3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="27"/>
+      <c r="C3" s="23"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12034,14 +12036,14 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="23"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="27"/>
+      <c r="C5" s="23"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -12050,7 +12052,7 @@
       <c r="B6" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="23"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -12059,7 +12061,7 @@
       <c r="B7" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="23"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -12068,7 +12070,7 @@
       <c r="B8" s="13">
         <v>4</v>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="23"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -12077,7 +12079,7 @@
       <c r="B9" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="27"/>
+      <c r="C9" s="23"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -12086,77 +12088,77 @@
       <c r="B10" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="23"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="25" t="s">
         <v>308</v>
       </c>
-      <c r="C12" s="30"/>
+      <c r="C12" s="26"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="25" t="s">
         <v>309</v>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="26"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="C14" s="30"/>
+      <c r="C14" s="26"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="25" t="s">
         <v>311</v>
       </c>
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="25" t="s">
         <v>312</v>
       </c>
-      <c r="C16" s="30"/>
+      <c r="C16" s="26"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="25" t="s">
         <v>313</v>
       </c>
-      <c r="C17" s="30"/>
+      <c r="C17" s="26"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="24" t="s">
         <v>300</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="25" t="s">
         <v>314</v>
       </c>
-      <c r="C18" s="30"/>
+      <c r="C18" s="26"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -12200,10 +12202,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12215,7 +12217,7 @@
       <c r="B2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12224,7 +12226,7 @@
       <c r="B3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12233,21 +12235,21 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -12256,7 +12258,7 @@
       <c r="B7" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -12265,7 +12267,7 @@
       <c r="B8" s="13">
         <v>6</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -12274,7 +12276,7 @@
       <c r="B9" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -12283,59 +12285,59 @@
       <c r="B10" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -12378,10 +12380,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12393,7 +12395,7 @@
       <c r="B2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12402,7 +12404,7 @@
       <c r="B3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12411,35 +12413,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -12448,7 +12450,7 @@
       <c r="B9" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -12457,59 +12459,59 @@
       <c r="B10" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -12552,10 +12554,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12567,7 +12569,7 @@
       <c r="B2" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12576,7 +12578,7 @@
       <c r="B3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12585,14 +12587,14 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -12601,21 +12603,21 @@
       <c r="B6" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -12624,7 +12626,7 @@
       <c r="B9" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -12633,59 +12635,59 @@
       <c r="B10" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -12728,10 +12730,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12743,7 +12745,7 @@
       <c r="B2" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12752,7 +12754,7 @@
       <c r="B3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12761,35 +12763,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -12798,7 +12800,7 @@
       <c r="B9" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -12807,59 +12809,59 @@
       <c r="B10" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -12902,10 +12904,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12917,7 +12919,7 @@
       <c r="B2" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12926,7 +12928,7 @@
       <c r="B3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12935,21 +12937,21 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -12958,7 +12960,7 @@
       <c r="B7" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -12967,7 +12969,7 @@
       <c r="B8" s="13">
         <v>5</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -12976,7 +12978,7 @@
       <c r="B9" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -12985,59 +12987,59 @@
       <c r="B10" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -13080,10 +13082,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -13095,7 +13097,7 @@
       <c r="B2" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -13104,7 +13106,7 @@
       <c r="B3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -13113,14 +13115,14 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -13129,7 +13131,7 @@
       <c r="B6" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -13138,7 +13140,7 @@
       <c r="B7" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -13147,7 +13149,7 @@
       <c r="B8" s="13">
         <v>3</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -13156,7 +13158,7 @@
       <c r="B9" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -13165,59 +13167,59 @@
       <c r="B10" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -13260,10 +13262,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -13275,7 +13277,7 @@
       <c r="B2" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -13284,7 +13286,7 @@
       <c r="B3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -13293,21 +13295,21 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -13316,7 +13318,7 @@
       <c r="B7" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -13325,7 +13327,7 @@
       <c r="B8" s="13">
         <v>6</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -13334,7 +13336,7 @@
       <c r="B9" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -13343,59 +13345,59 @@
       <c r="B10" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -13438,10 +13440,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -13453,7 +13455,7 @@
       <c r="B2" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -13462,7 +13464,7 @@
       <c r="B3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="27"/>
+      <c r="C3" s="23"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -13471,14 +13473,14 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="23"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="27"/>
+      <c r="C5" s="23"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -13487,7 +13489,7 @@
       <c r="B6" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="23"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -13496,7 +13498,7 @@
       <c r="B7" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="23"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -13505,7 +13507,7 @@
       <c r="B8" s="13">
         <v>3</v>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="23"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -13514,7 +13516,7 @@
       <c r="B9" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="C9" s="27"/>
+      <c r="C9" s="23"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -13523,77 +13525,77 @@
       <c r="B10" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="23"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="25" t="s">
         <v>315</v>
       </c>
-      <c r="C12" s="30"/>
+      <c r="C12" s="26"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="25" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="26"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="25" t="s">
         <v>317</v>
       </c>
-      <c r="C14" s="30"/>
+      <c r="C14" s="26"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="25" t="s">
         <v>318</v>
       </c>
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="25" t="s">
         <v>319</v>
       </c>
-      <c r="C16" s="30"/>
+      <c r="C16" s="26"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="25" t="s">
         <v>320</v>
       </c>
-      <c r="C17" s="30"/>
+      <c r="C17" s="26"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="24" t="s">
         <v>300</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="25" t="s">
         <v>321</v>
       </c>
-      <c r="C18" s="30"/>
+      <c r="C18" s="26"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -13636,10 +13638,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -13651,7 +13653,7 @@
       <c r="B2" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -13660,7 +13662,7 @@
       <c r="B3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -13669,14 +13671,14 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -13685,21 +13687,21 @@
       <c r="B6" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -13708,7 +13710,7 @@
       <c r="B9" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -13717,59 +13719,59 @@
       <c r="B10" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -13812,10 +13814,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -13827,7 +13829,7 @@
       <c r="B2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -13836,7 +13838,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -13845,7 +13847,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -13854,28 +13856,28 @@
       <c r="B5" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -13884,7 +13886,7 @@
       <c r="B9" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -13893,59 +13895,59 @@
       <c r="B10" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -13988,10 +13990,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -14003,7 +14005,7 @@
       <c r="B2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -14012,7 +14014,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -14021,7 +14023,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -14030,7 +14032,7 @@
       <c r="B5" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -14039,21 +14041,21 @@
       <c r="B6" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -14062,7 +14064,7 @@
       <c r="B9" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -14071,59 +14073,59 @@
       <c r="B10" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -14166,10 +14168,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -14181,7 +14183,7 @@
       <c r="B2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -14190,7 +14192,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -14199,7 +14201,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -14208,7 +14210,7 @@
       <c r="B5" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -14217,7 +14219,7 @@
       <c r="B6" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -14226,7 +14228,7 @@
       <c r="B7" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -14235,7 +14237,7 @@
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -14244,7 +14246,7 @@
       <c r="B9" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -14253,59 +14255,59 @@
       <c r="B10" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -14348,10 +14350,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -14363,7 +14365,7 @@
       <c r="B2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -14372,7 +14374,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -14381,7 +14383,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -14390,28 +14392,28 @@
       <c r="B5" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -14420,7 +14422,7 @@
       <c r="B9" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -14429,59 +14431,59 @@
       <c r="B10" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="15"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">

--- a/customer-stories/Customer_Stories_PlanB.xlsx
+++ b/customer-stories/Customer_Stories_PlanB.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="335">
   <si>
     <t>#</t>
   </si>
@@ -11608,8 +11608,12 @@
       <c r="B15" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="29"/>
+      <c r="C15" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="21" t="s">
@@ -11618,8 +11622,12 @@
       <c r="B16" s="22" t="s">
         <v>298</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="29"/>
+      <c r="C16" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="21" t="s">

--- a/customer-stories/Customer_Stories_PlanB.xlsx
+++ b/customer-stories/Customer_Stories_PlanB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flaviamendeztsutsumi/Desktop/ISO/ISW-Practica/customer-stories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43FAEB3-E4A2-E14D-8A10-77628B36ECEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96338555-2CDF-CB43-A315-E19D4BE48F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" firstSheet="41" activeTab="47" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4300" yWindow="680" windowWidth="29900" windowHeight="19900" firstSheet="42" activeTab="47" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="351">
   <si>
     <t>#</t>
   </si>
@@ -1129,6 +1129,9 @@
   </si>
   <si>
     <t xml:space="preserve">Pantalla de perfil en el frontend </t>
+  </si>
+  <si>
+    <t>8 min</t>
   </si>
 </sst>
 </file>
@@ -1464,9 +1467,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1504,12 +1504,6 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1518,6 +1512,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4246,13 +4249,13 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="38">
+      <c r="A60" s="37">
         <v>59</v>
       </c>
-      <c r="B60" s="38" t="s">
+      <c r="B60" s="37" t="s">
         <v>335</v>
       </c>
-      <c r="C60" s="37"/>
+      <c r="C60" s="36"/>
       <c r="D60" s="9" t="s">
         <v>336</v>
       </c>
@@ -4334,10 +4337,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -4349,7 +4352,7 @@
       <c r="B2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -4358,7 +4361,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -4367,7 +4370,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -4376,28 +4379,28 @@
       <c r="B5" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -4406,7 +4409,7 @@
       <c r="B9" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -4415,59 +4418,59 @@
       <c r="B10" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -4509,10 +4512,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -4524,7 +4527,7 @@
       <c r="B2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -4533,7 +4536,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -4542,7 +4545,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -4551,7 +4554,7 @@
       <c r="B5" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -4560,7 +4563,7 @@
       <c r="B6" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -4569,7 +4572,7 @@
       <c r="B7" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -4578,7 +4581,7 @@
       <c r="B8" s="11">
         <v>7</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -4587,7 +4590,7 @@
       <c r="B9" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -4596,59 +4599,59 @@
       <c r="B10" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -4690,10 +4693,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -4705,7 +4708,7 @@
       <c r="B2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -4714,7 +4717,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -4723,7 +4726,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -4732,7 +4735,7 @@
       <c r="B5" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -4741,7 +4744,7 @@
       <c r="B6" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -4750,7 +4753,7 @@
       <c r="B7" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -4759,7 +4762,7 @@
       <c r="B8" s="11">
         <v>20</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -4768,7 +4771,7 @@
       <c r="B9" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -4777,59 +4780,59 @@
       <c r="B10" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -4871,10 +4874,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -4886,7 +4889,7 @@
       <c r="B2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -4895,7 +4898,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -4904,7 +4907,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -4913,28 +4916,28 @@
       <c r="B5" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -4943,7 +4946,7 @@
       <c r="B9" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -4952,59 +4955,59 @@
       <c r="B10" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5046,10 +5049,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5061,7 +5064,7 @@
       <c r="B2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5070,7 +5073,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5079,7 +5082,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5088,7 +5091,7 @@
       <c r="B5" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -5097,7 +5100,7 @@
       <c r="B6" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -5106,7 +5109,7 @@
       <c r="B7" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -5115,7 +5118,7 @@
       <c r="B8" s="11">
         <v>20</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -5124,7 +5127,7 @@
       <c r="B9" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -5133,59 +5136,59 @@
       <c r="B10" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5227,10 +5230,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5242,7 +5245,7 @@
       <c r="B2" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5251,7 +5254,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5260,7 +5263,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5269,7 +5272,7 @@
       <c r="B5" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -5278,7 +5281,7 @@
       <c r="B6" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -5287,7 +5290,7 @@
       <c r="B7" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -5296,7 +5299,7 @@
       <c r="B8" s="11">
         <v>20</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -5305,7 +5308,7 @@
       <c r="B9" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -5314,59 +5317,59 @@
       <c r="B10" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5408,10 +5411,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5423,7 +5426,7 @@
       <c r="B2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5432,7 +5435,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5441,7 +5444,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5450,28 +5453,28 @@
       <c r="B5" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -5480,7 +5483,7 @@
       <c r="B9" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -5489,59 +5492,59 @@
       <c r="B10" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5583,10 +5586,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5598,7 +5601,7 @@
       <c r="B2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5607,7 +5610,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5616,7 +5619,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5625,28 +5628,28 @@
       <c r="B5" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -5655,7 +5658,7 @@
       <c r="B9" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -5664,59 +5667,59 @@
       <c r="B10" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5758,10 +5761,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5773,7 +5776,7 @@
       <c r="B2" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5782,7 +5785,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5791,7 +5794,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5800,7 +5803,7 @@
       <c r="B5" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -5809,7 +5812,7 @@
       <c r="B6" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -5818,7 +5821,7 @@
       <c r="B7" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -5827,7 +5830,7 @@
       <c r="B8" s="11">
         <v>40</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -5836,7 +5839,7 @@
       <c r="B9" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -5845,59 +5848,59 @@
       <c r="B10" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -5939,10 +5942,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -5954,7 +5957,7 @@
       <c r="B2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -5963,7 +5966,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -5972,7 +5975,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -5981,28 +5984,28 @@
       <c r="B5" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6011,7 +6014,7 @@
       <c r="B9" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6020,59 +6023,59 @@
       <c r="B10" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6114,10 +6117,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -6129,7 +6132,7 @@
       <c r="B2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -6138,7 +6141,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -6147,7 +6150,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -6156,28 +6159,28 @@
       <c r="B5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6186,7 +6189,7 @@
       <c r="B9" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6195,59 +6198,59 @@
       <c r="B10" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6289,10 +6292,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -6304,7 +6307,7 @@
       <c r="B2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -6313,7 +6316,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -6322,7 +6325,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -6331,28 +6334,28 @@
       <c r="B5" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6361,7 +6364,7 @@
       <c r="B9" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6370,59 +6373,59 @@
       <c r="B10" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6464,10 +6467,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -6479,7 +6482,7 @@
       <c r="B2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -6488,7 +6491,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -6497,7 +6500,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -6506,7 +6509,7 @@
       <c r="B5" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -6515,7 +6518,7 @@
       <c r="B6" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -6524,7 +6527,7 @@
       <c r="B7" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -6533,7 +6536,7 @@
       <c r="B8" s="11">
         <v>5</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6542,7 +6545,7 @@
       <c r="B9" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6551,59 +6554,59 @@
       <c r="B10" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6645,10 +6648,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -6660,7 +6663,7 @@
       <c r="B2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -6669,7 +6672,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -6678,7 +6681,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -6687,28 +6690,28 @@
       <c r="B5" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6717,7 +6720,7 @@
       <c r="B9" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6726,59 +6729,59 @@
       <c r="B10" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6820,10 +6823,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -6835,7 +6838,7 @@
       <c r="B2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -6844,7 +6847,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -6853,21 +6856,21 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -6876,7 +6879,7 @@
       <c r="B7" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -6885,7 +6888,7 @@
       <c r="B8" s="13">
         <v>7</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -6894,7 +6897,7 @@
       <c r="B9" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -6903,59 +6906,59 @@
       <c r="B10" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -6997,10 +7000,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7012,7 +7015,7 @@
       <c r="B2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7021,7 +7024,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7030,35 +7033,35 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7067,7 +7070,7 @@
       <c r="B9" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7076,59 +7079,59 @@
       <c r="B10" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -7170,10 +7173,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7185,7 +7188,7 @@
       <c r="B2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7194,7 +7197,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7203,21 +7206,21 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -7226,7 +7229,7 @@
       <c r="B7" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -7235,7 +7238,7 @@
       <c r="B8" s="13">
         <v>8</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7244,7 +7247,7 @@
       <c r="B9" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7253,59 +7256,59 @@
       <c r="B10" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -7347,10 +7350,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7362,7 +7365,7 @@
       <c r="B2" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7371,7 +7374,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7380,21 +7383,21 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -7403,7 +7406,7 @@
       <c r="B7" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -7412,7 +7415,7 @@
       <c r="B8" s="13">
         <v>10</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7421,7 +7424,7 @@
       <c r="B9" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7430,59 +7433,59 @@
       <c r="B10" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -7524,10 +7527,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7539,7 +7542,7 @@
       <c r="B2" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7548,7 +7551,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7557,14 +7560,14 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -7573,7 +7576,7 @@
       <c r="B6" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -7582,7 +7585,7 @@
       <c r="B7" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -7591,7 +7594,7 @@
       <c r="B8" s="11">
         <v>20</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7600,7 +7603,7 @@
       <c r="B9" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7609,59 +7612,59 @@
       <c r="B10" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -7703,10 +7706,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7718,7 +7721,7 @@
       <c r="B2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7727,7 +7730,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7736,14 +7739,14 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -7752,7 +7755,7 @@
       <c r="B6" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -7761,7 +7764,7 @@
       <c r="B7" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -7770,7 +7773,7 @@
       <c r="B8" s="13">
         <v>13</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7779,7 +7782,7 @@
       <c r="B9" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7788,59 +7791,59 @@
       <c r="B10" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -7882,10 +7885,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -7897,7 +7900,7 @@
       <c r="B2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -7906,7 +7909,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -7915,21 +7918,21 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -7938,7 +7941,7 @@
       <c r="B7" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -7947,7 +7950,7 @@
       <c r="B8" s="13">
         <v>6</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -7956,7 +7959,7 @@
       <c r="B9" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -7965,59 +7968,59 @@
       <c r="B10" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8059,10 +8062,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8074,7 +8077,7 @@
       <c r="B2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8083,7 +8086,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8092,7 +8095,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -8101,28 +8104,28 @@
       <c r="B5" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -8131,7 +8134,7 @@
       <c r="B9" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -8140,59 +8143,59 @@
       <c r="B10" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8234,10 +8237,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8249,7 +8252,7 @@
       <c r="B2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8258,7 +8261,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8267,14 +8270,14 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -8283,21 +8286,21 @@
       <c r="B6" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -8306,7 +8309,7 @@
       <c r="B9" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -8315,59 +8318,59 @@
       <c r="B10" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8409,10 +8412,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8424,7 +8427,7 @@
       <c r="B2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8433,7 +8436,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8442,14 +8445,14 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -8458,7 +8461,7 @@
       <c r="B6" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -8467,7 +8470,7 @@
       <c r="B7" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -8476,7 +8479,7 @@
       <c r="B8" s="13">
         <v>7</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -8485,7 +8488,7 @@
       <c r="B9" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -8494,59 +8497,59 @@
       <c r="B10" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8588,10 +8591,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8603,7 +8606,7 @@
       <c r="B2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8612,7 +8615,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8621,35 +8624,35 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -8658,7 +8661,7 @@
       <c r="B9" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -8667,59 +8670,59 @@
       <c r="B10" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8761,10 +8764,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8776,7 +8779,7 @@
       <c r="B2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8785,7 +8788,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8794,14 +8797,14 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -8810,7 +8813,7 @@
       <c r="B6" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -8819,7 +8822,7 @@
       <c r="B7" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -8828,7 +8831,7 @@
       <c r="B8" s="11">
         <v>8</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -8837,7 +8840,7 @@
       <c r="B9" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -8846,59 +8849,59 @@
       <c r="B10" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -8940,10 +8943,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -8955,7 +8958,7 @@
       <c r="B2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -8964,7 +8967,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -8973,14 +8976,14 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -8989,7 +8992,7 @@
       <c r="B6" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -8998,7 +9001,7 @@
       <c r="B7" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -9007,7 +9010,7 @@
       <c r="B8" s="13">
         <v>4</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9016,7 +9019,7 @@
       <c r="B9" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9025,59 +9028,59 @@
       <c r="B10" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9119,10 +9122,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -9134,7 +9137,7 @@
       <c r="B2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -9143,7 +9146,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -9152,35 +9155,35 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9189,7 +9192,7 @@
       <c r="B9" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9198,59 +9201,59 @@
       <c r="B10" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9292,10 +9295,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -9307,7 +9310,7 @@
       <c r="B2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -9316,7 +9319,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -9325,14 +9328,14 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -9341,7 +9344,7 @@
       <c r="B6" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -9350,7 +9353,7 @@
       <c r="B7" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -9359,7 +9362,7 @@
       <c r="B8" s="11">
         <v>8</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9368,7 +9371,7 @@
       <c r="B9" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9377,59 +9380,59 @@
       <c r="B10" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9471,10 +9474,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -9486,7 +9489,7 @@
       <c r="B2" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -9495,7 +9498,7 @@
       <c r="B3" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -9504,14 +9507,14 @@
       <c r="B4" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -9520,7 +9523,7 @@
       <c r="B6" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -9529,7 +9532,7 @@
       <c r="B7" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -9538,7 +9541,7 @@
       <c r="B8" s="13">
         <v>6</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9547,7 +9550,7 @@
       <c r="B9" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9556,59 +9559,59 @@
       <c r="B10" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9650,10 +9653,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -9665,7 +9668,7 @@
       <c r="B2" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -9674,14 +9677,14 @@
       <c r="B3" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -9690,28 +9693,28 @@
       <c r="B5" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9720,7 +9723,7 @@
       <c r="B9" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9729,59 +9732,59 @@
       <c r="B10" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9823,10 +9826,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -9838,7 +9841,7 @@
       <c r="B2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -9847,14 +9850,14 @@
       <c r="B3" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -9863,28 +9866,28 @@
       <c r="B5" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -9893,7 +9896,7 @@
       <c r="B9" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -9902,59 +9905,59 @@
       <c r="B10" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -9996,10 +9999,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10011,7 +10014,7 @@
       <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10020,7 +10023,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -10029,7 +10032,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -10038,28 +10041,28 @@
       <c r="B5" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10068,7 +10071,7 @@
       <c r="B9" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10077,59 +10080,59 @@
       <c r="B10" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10171,10 +10174,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10186,7 +10189,7 @@
       <c r="B2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10195,14 +10198,14 @@
       <c r="B3" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -10211,28 +10214,28 @@
       <c r="B5" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10241,7 +10244,7 @@
       <c r="B9" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10250,59 +10253,59 @@
       <c r="B10" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10344,10 +10347,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10359,7 +10362,7 @@
       <c r="B2" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10368,14 +10371,14 @@
       <c r="B3" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -10384,14 +10387,14 @@
       <c r="B5" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -10400,7 +10403,7 @@
       <c r="B7" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -10409,7 +10412,7 @@
       <c r="B8" s="13">
         <v>5</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10418,7 +10421,7 @@
       <c r="B9" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10427,59 +10430,59 @@
       <c r="B10" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10521,10 +10524,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10536,7 +10539,7 @@
       <c r="B2" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10545,14 +10548,14 @@
       <c r="B3" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -10561,28 +10564,28 @@
       <c r="B5" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10591,7 +10594,7 @@
       <c r="B9" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10600,59 +10603,59 @@
       <c r="B10" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10694,10 +10697,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10709,7 +10712,7 @@
       <c r="B2" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10718,14 +10721,14 @@
       <c r="B3" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -10734,14 +10737,14 @@
       <c r="B5" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -10750,7 +10753,7 @@
       <c r="B7" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -10759,7 +10762,7 @@
       <c r="B8" s="13">
         <v>10</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10768,7 +10771,7 @@
       <c r="B9" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10777,59 +10780,59 @@
       <c r="B10" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -10871,10 +10874,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -10886,7 +10889,7 @@
       <c r="B2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -10895,7 +10898,7 @@
       <c r="B3" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -10904,35 +10907,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -10941,7 +10944,7 @@
       <c r="B9" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -10950,59 +10953,59 @@
       <c r="B10" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -11044,10 +11047,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -11059,7 +11062,7 @@
       <c r="B2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -11068,7 +11071,7 @@
       <c r="B3" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -11077,14 +11080,14 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -11093,21 +11096,21 @@
       <c r="B6" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -11116,7 +11119,7 @@
       <c r="B9" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -11125,59 +11128,59 @@
       <c r="B10" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -11219,10 +11222,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -11234,7 +11237,7 @@
       <c r="B2" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -11243,7 +11246,7 @@
       <c r="B3" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -11252,35 +11255,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -11289,7 +11292,7 @@
       <c r="B9" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -11298,59 +11301,59 @@
       <c r="B10" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -11392,10 +11395,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -11407,7 +11410,7 @@
       <c r="B2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -11416,7 +11419,7 @@
       <c r="B3" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -11425,35 +11428,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -11462,7 +11465,7 @@
       <c r="B9" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -11471,59 +11474,59 @@
       <c r="B10" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -11567,10 +11570,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -11674,7 +11677,7 @@
       <c r="C12" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="28" t="s">
         <v>272</v>
       </c>
     </row>
@@ -11685,10 +11688,10 @@
       <c r="B13" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="29" t="s">
         <v>274</v>
       </c>
     </row>
@@ -11702,7 +11705,7 @@
       <c r="C14" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="28" t="s">
         <v>276</v>
       </c>
     </row>
@@ -11716,7 +11719,7 @@
       <c r="C15" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="28" t="s">
         <v>272</v>
       </c>
     </row>
@@ -11730,7 +11733,7 @@
       <c r="C16" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="28" t="s">
         <v>272</v>
       </c>
     </row>
@@ -11742,7 +11745,7 @@
         <v>279</v>
       </c>
       <c r="C17" s="17"/>
-      <c r="D17" s="29"/>
+      <c r="D17" s="28"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21" t="s">
@@ -11754,7 +11757,7 @@
       <c r="C18" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="29" t="s">
         <v>282</v>
       </c>
     </row>
@@ -11765,8 +11768,12 @@
       <c r="B19" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="29"/>
+      <c r="C19" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="21" t="s">
@@ -11778,7 +11785,7 @@
       <c r="C20" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="28" t="s">
         <v>287</v>
       </c>
     </row>
@@ -11789,8 +11796,8 @@
       <c r="B21" s="22" t="s">
         <v>289</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="28"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
@@ -11799,10 +11806,10 @@
       <c r="B22" s="22" t="s">
         <v>349</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="41" t="s">
         <v>276</v>
       </c>
     </row>
@@ -11845,10 +11852,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -11860,7 +11867,7 @@
       <c r="B2" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -11869,7 +11876,7 @@
       <c r="B3" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -11878,35 +11885,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -11915,7 +11922,7 @@
       <c r="B9" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -11924,59 +11931,59 @@
       <c r="B10" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -12018,10 +12025,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12033,7 +12040,7 @@
       <c r="B2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12042,7 +12049,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12051,7 +12058,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -12060,7 +12067,7 @@
       <c r="B5" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -12069,7 +12076,7 @@
       <c r="B6" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -12078,7 +12085,7 @@
       <c r="B7" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -12087,7 +12094,7 @@
       <c r="B8" s="11">
         <v>5</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -12096,7 +12103,7 @@
       <c r="B9" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -12105,59 +12112,59 @@
       <c r="B10" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -12200,10 +12207,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12433,10 +12440,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12448,7 +12455,7 @@
       <c r="B2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12457,7 +12464,7 @@
       <c r="B3" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12466,21 +12473,21 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -12489,7 +12496,7 @@
       <c r="B7" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -12498,7 +12505,7 @@
       <c r="B8" s="13">
         <v>6</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -12507,7 +12514,7 @@
       <c r="B9" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -12516,59 +12523,59 @@
       <c r="B10" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -12610,10 +12617,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12625,7 +12632,7 @@
       <c r="B2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12634,7 +12641,7 @@
       <c r="B3" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12643,35 +12650,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -12680,7 +12687,7 @@
       <c r="B9" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -12689,59 +12696,59 @@
       <c r="B10" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -12783,10 +12790,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12798,7 +12805,7 @@
       <c r="B2" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12807,7 +12814,7 @@
       <c r="B3" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12816,14 +12823,14 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -12832,21 +12839,21 @@
       <c r="B6" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -12855,7 +12862,7 @@
       <c r="B9" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -12864,59 +12871,59 @@
       <c r="B10" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -12958,10 +12965,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12973,7 +12980,7 @@
       <c r="B2" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -12982,7 +12989,7 @@
       <c r="B3" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -12991,35 +12998,35 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -13028,7 +13035,7 @@
       <c r="B9" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -13037,59 +13044,59 @@
       <c r="B10" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -13131,10 +13138,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -13146,7 +13153,7 @@
       <c r="B2" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -13155,7 +13162,7 @@
       <c r="B3" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -13164,21 +13171,21 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -13187,7 +13194,7 @@
       <c r="B7" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -13196,7 +13203,7 @@
       <c r="B8" s="13">
         <v>5</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -13205,7 +13212,7 @@
       <c r="B9" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -13214,59 +13221,59 @@
       <c r="B10" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -13308,10 +13315,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -13323,7 +13330,7 @@
       <c r="B2" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -13332,7 +13339,7 @@
       <c r="B3" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -13341,14 +13348,14 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -13357,7 +13364,7 @@
       <c r="B6" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -13366,7 +13373,7 @@
       <c r="B7" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -13375,7 +13382,7 @@
       <c r="B8" s="13">
         <v>3</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -13384,7 +13391,7 @@
       <c r="B9" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -13393,59 +13400,59 @@
       <c r="B10" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -13487,10 +13494,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -13502,7 +13509,7 @@
       <c r="B2" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -13511,7 +13518,7 @@
       <c r="B3" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -13520,21 +13527,21 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -13543,7 +13550,7 @@
       <c r="B7" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -13552,7 +13559,7 @@
       <c r="B8" s="13">
         <v>6</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -13561,7 +13568,7 @@
       <c r="B9" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -13570,59 +13577,59 @@
       <c r="B10" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -13665,10 +13672,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -13881,10 +13888,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -13896,7 +13903,7 @@
       <c r="B2" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -13905,7 +13912,7 @@
       <c r="B3" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -13914,14 +13921,14 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -13930,21 +13937,21 @@
       <c r="B6" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -13953,7 +13960,7 @@
       <c r="B9" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -13962,59 +13969,59 @@
       <c r="B10" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -14056,10 +14063,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -14071,7 +14078,7 @@
       <c r="B2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -14080,7 +14087,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -14089,7 +14096,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -14098,28 +14105,28 @@
       <c r="B5" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -14128,7 +14135,7 @@
       <c r="B9" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -14137,59 +14144,59 @@
       <c r="B10" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -14232,187 +14239,187 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="32" t="s">
         <v>336</v>
       </c>
-      <c r="C2" s="33"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="33"/>
+      <c r="C3" s="32"/>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="32" t="s">
         <v>337</v>
       </c>
-      <c r="C4" s="33"/>
+      <c r="C4" s="32"/>
     </row>
     <row r="5" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="33"/>
+      <c r="C5" s="32"/>
     </row>
     <row r="6" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="33"/>
+      <c r="C6" s="32"/>
     </row>
     <row r="7" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="33"/>
+      <c r="C7" s="32"/>
     </row>
     <row r="8" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="32">
         <v>4</v>
       </c>
-      <c r="C8" s="33"/>
+      <c r="C8" s="32"/>
     </row>
     <row r="9" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="32" t="s">
         <v>338</v>
       </c>
-      <c r="C9" s="33"/>
+      <c r="C9" s="32"/>
     </row>
     <row r="10" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="32" t="s">
         <v>339</v>
       </c>
-      <c r="C10" s="33"/>
+      <c r="C10" s="32"/>
     </row>
     <row r="11" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="31" t="s">
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="30" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="32" t="s">
         <v>340</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="D12" s="40"/>
+      <c r="D12" s="39"/>
     </row>
     <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="D13" s="40"/>
+      <c r="D13" s="39"/>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="32" t="s">
         <v>342</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="D14" s="40"/>
+      <c r="D14" s="39"/>
     </row>
     <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="32" t="s">
         <v>343</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="39" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="32" t="s">
         <v>344</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="40"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="39"/>
     </row>
     <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="32" t="s">
         <v>345</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="40"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="39"/>
     </row>
     <row r="18" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="40"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="39"/>
     </row>
     <row r="19" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="38" t="s">
         <v>140</v>
       </c>
     </row>
@@ -14435,10 +14442,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -14450,7 +14457,7 @@
       <c r="B2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -14459,7 +14466,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -14468,7 +14475,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -14477,7 +14484,7 @@
       <c r="B5" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -14486,21 +14493,21 @@
       <c r="B6" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -14509,7 +14516,7 @@
       <c r="B9" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -14518,59 +14525,59 @@
       <c r="B10" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -14612,10 +14619,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -14627,7 +14634,7 @@
       <c r="B2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -14636,7 +14643,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -14645,7 +14652,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -14654,7 +14661,7 @@
       <c r="B5" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
@@ -14663,7 +14670,7 @@
       <c r="B6" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
@@ -14672,7 +14679,7 @@
       <c r="B7" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -14681,7 +14688,7 @@
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -14690,7 +14697,7 @@
       <c r="B9" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -14699,59 +14706,59 @@
       <c r="B10" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
@@ -14793,10 +14800,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
@@ -14808,7 +14815,7 @@
       <c r="B2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
@@ -14817,7 +14824,7 @@
       <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -14826,7 +14833,7 @@
       <c r="B4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -14835,28 +14842,28 @@
       <c r="B5" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -14865,7 +14872,7 @@
       <c r="B9" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
@@ -14874,59 +14881,59 @@
       <c r="B10" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="11"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="42"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="42"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="11"/>
-      <c r="C15" s="42"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="11"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="42"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">

--- a/customer-stories/Customer_Stories_PlanB.xlsx
+++ b/customer-stories/Customer_Stories_PlanB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciaguzman/Desktop/ISW-Practica-1/customer-stories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B59033A-F969-2E4D-9697-2C4D8A312054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2FCE3A-CBE9-FB49-85AF-9BACA468615C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" firstSheet="44" activeTab="47" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" firstSheet="44" activeTab="47" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="354">
   <si>
     <t>#</t>
   </si>
@@ -11760,9 +11760,11 @@
       <c r="B17" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="C17" s="17"/>
+      <c r="C17" s="42" t="s">
+        <v>271</v>
+      </c>
       <c r="D17" s="29" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
